--- a/shared/data/烟箱信息汇总完整版.xlsx
+++ b/shared/data/烟箱信息汇总完整版.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="843">
   <si>
     <t xml:space="preserve">品名</t>
   </si>
@@ -286,6 +286,9 @@
     <t xml:space="preserve">（91）107396121307012602100495457748</t>
   </si>
   <si>
+    <t xml:space="preserve">5*6</t>
+  </si>
+  <si>
     <t xml:space="preserve">长白山（蓝尚）</t>
   </si>
   <si>
@@ -299,9 +302,6 @@
   </si>
   <si>
     <t xml:space="preserve">098342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5*6</t>
   </si>
   <si>
     <t xml:space="preserve">中南海（冰耀中支）</t>
@@ -2654,27 +2654,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3339,31 +3339,33 @@
       <c r="G17" s="3" t="n">
         <v>107396</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I18" s="3"/>
     </row>
@@ -3387,7 +3389,9 @@
       <c r="G19" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="I19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3411,7 +3415,7 @@
         <v>102</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I20" s="3"/>
     </row>
@@ -3501,7 +3505,7 @@
         <v>212892</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I24" s="3"/>
     </row>
@@ -3513,7 +3517,7 @@
         <v>119</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>12</v>
@@ -3588,7 +3592,7 @@
         <v>132</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>12</v>
@@ -3626,7 +3630,7 @@
         <v>139</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I29" s="3"/>
     </row>
@@ -3776,7 +3780,7 @@
         <v>115131</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I35" s="3"/>
     </row>
@@ -3901,7 +3905,7 @@
         <v>190</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I40" s="3"/>
     </row>
@@ -4080,7 +4084,9 @@
       <c r="G48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H48" s="3"/>
+      <c r="H48" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4104,7 +4110,7 @@
         <v>223</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I49" s="3"/>
     </row>
@@ -4129,7 +4135,7 @@
         <v>228</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I50" s="3"/>
     </row>
@@ -4154,7 +4160,7 @@
         <v>233</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I51" s="3"/>
     </row>
@@ -4179,7 +4185,7 @@
         <v>143547</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I52" s="3"/>
     </row>
@@ -4419,7 +4425,7 @@
         <v>280</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I62" s="3"/>
     </row>
@@ -4519,7 +4525,7 @@
         <v>298</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I66" s="3"/>
     </row>
@@ -4557,7 +4563,7 @@
       <c r="F68" s="3"/>
       <c r="G68" s="4"/>
       <c r="H68" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I68" s="3"/>
     </row>
@@ -4580,7 +4586,7 @@
       <c r="F69" s="3"/>
       <c r="G69" s="4"/>
       <c r="H69" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I69" s="3"/>
     </row>
@@ -4630,7 +4636,7 @@
         <v>318</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I71" s="3"/>
     </row>
@@ -4680,7 +4686,7 @@
         <v>327</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I73" s="3"/>
     </row>
@@ -4948,7 +4954,7 @@
         <v>372</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I85" s="3"/>
     </row>
@@ -4973,7 +4979,7 @@
         <v>252973</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I86" s="3"/>
     </row>
@@ -5028,7 +5034,7 @@
         <v>384</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I89" s="3"/>
     </row>
@@ -5078,7 +5084,7 @@
         <v>393</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I91" s="3"/>
     </row>
@@ -5311,7 +5317,7 @@
         <v>271011</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I102" s="3"/>
     </row>
@@ -5451,7 +5457,7 @@
         <v>457</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -5565,7 +5571,9 @@
       <c r="G113" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="H113" s="3"/>
+      <c r="H113" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="I113" s="3"/>
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5797,7 +5805,7 @@
         <v>518</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I124" s="3"/>
     </row>
@@ -5822,7 +5830,7 @@
         <v>522</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I125" s="3"/>
     </row>
@@ -5847,7 +5855,7 @@
         <v>145084</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I126" s="3"/>
     </row>
@@ -6002,7 +6010,7 @@
         <v>555</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I133" s="3"/>
     </row>
@@ -6117,7 +6125,7 @@
         <v>268998</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I138" s="3"/>
     </row>
@@ -6262,7 +6270,7 @@
         <v>600</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I145" s="3"/>
     </row>
@@ -6287,7 +6295,7 @@
         <v>605</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I146" s="3"/>
     </row>
@@ -6337,7 +6345,7 @@
         <v>615</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I148" s="3"/>
     </row>
@@ -6402,7 +6410,7 @@
         <v>627</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I151" s="3"/>
     </row>
@@ -6452,7 +6460,7 @@
         <v>636</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I153" s="3"/>
     </row>
@@ -6477,7 +6485,7 @@
         <v>641</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I154" s="3"/>
     </row>
@@ -6525,7 +6533,7 @@
       <c r="F156" s="3"/>
       <c r="G156" s="4"/>
       <c r="H156" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I156" s="3"/>
     </row>
@@ -6560,7 +6568,7 @@
         <v>655</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>12</v>
@@ -6573,7 +6581,7 @@
         <v>657</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I158" s="3"/>
     </row>
@@ -6621,7 +6629,7 @@
       <c r="F160" s="3"/>
       <c r="G160" s="4"/>
       <c r="H160" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I160" s="3"/>
     </row>
@@ -6671,7 +6679,7 @@
         <v>674</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I162" s="3"/>
     </row>
@@ -6771,7 +6779,7 @@
         <v>693</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I166" s="3"/>
     </row>
@@ -6796,7 +6804,7 @@
         <v>698</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I167" s="3"/>
     </row>
@@ -6896,7 +6904,7 @@
         <v>716</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I171" s="3"/>
     </row>
@@ -7021,7 +7029,7 @@
         <v>740</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I176" s="3"/>
     </row>
@@ -7046,7 +7054,7 @@
         <v>745</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I177" s="3"/>
     </row>
@@ -7170,7 +7178,9 @@
       <c r="G182" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="H182" s="3"/>
+      <c r="H182" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I182" s="3"/>
     </row>
     <row r="183" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7217,7 +7227,7 @@
         <v>777</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I184" s="3"/>
     </row>
@@ -7290,7 +7300,7 @@
       <c r="F187" s="3"/>
       <c r="G187" s="4"/>
       <c r="H187" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I187" s="3"/>
     </row>
@@ -7536,7 +7546,7 @@
         <v>834</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I197" s="3"/>
     </row>
@@ -7561,7 +7571,7 @@
         <v>838</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I198" s="3"/>
     </row>
@@ -7584,7 +7594,7 @@
       <c r="F199" s="3"/>
       <c r="G199" s="4"/>
       <c r="H199" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I199" s="3"/>
     </row>
